--- a/StructureDefinition-QuestionnaireResponseLE.xlsx
+++ b/StructureDefinition-QuestionnaireResponseLE.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-QuestionnaireResponseLE.xlsx
+++ b/StructureDefinition-QuestionnaireResponseLE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="293">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -808,6 +808,9 @@
     <t>Items can repeat in the answers, so a direct 1..1 correspondence by position might not exist - requiring correspondence by identifier.</t>
   </si>
   <si>
+    <t>resumen</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode=DEFN].target[classCode=OBS, moodCode=DEFN].id</t>
   </si>
   <si>
@@ -840,6 +843,9 @@
   </si>
   <si>
     <t>Allows the questionnaire response to be read without access to the questionnaire.</t>
+  </si>
+  <si>
+    <t>Resumen</t>
   </si>
   <si>
     <t>.text</t>
@@ -3917,7 +3923,7 @@
         <v>74</v>
       </c>
       <c r="R25" t="s" s="2">
-        <v>74</v>
+        <v>253</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -3974,7 +3980,7 @@
         <v>74</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
@@ -3982,7 +3988,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4008,16 +4014,16 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O26" t="s" s="2">
         <v>74</v>
@@ -4066,7 +4072,7 @@
         <v>74</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>72</v>
@@ -4084,7 +4090,7 @@
         <v>74</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>74</v>
@@ -4092,7 +4098,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4118,14 +4124,14 @@
         <v>236</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O27" t="s" s="2">
         <v>74</v>
@@ -4135,7 +4141,7 @@
         <v>74</v>
       </c>
       <c r="R27" t="s" s="2">
-        <v>74</v>
+        <v>265</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>74</v>
@@ -4174,7 +4180,7 @@
         <v>74</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>72</v>
@@ -4192,7 +4198,7 @@
         <v>74</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>74</v>
@@ -4200,7 +4206,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4226,13 +4232,13 @@
         <v>229</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
@@ -4282,7 +4288,7 @@
         <v>74</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>72</v>
@@ -4300,7 +4306,7 @@
         <v>74</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>74</v>
@@ -4308,7 +4314,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4414,7 +4420,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -4522,7 +4528,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -4632,7 +4638,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -4655,19 +4661,19 @@
         <v>74</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>74</v>
@@ -4692,13 +4698,13 @@
         <v>74</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>74</v>
@@ -4716,7 +4722,7 @@
         <v>74</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>72</v>
@@ -4734,7 +4740,7 @@
         <v>74</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>74</v>
@@ -4742,7 +4748,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -4768,14 +4774,14 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>74</v>
@@ -4824,7 +4830,7 @@
         <v>74</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>72</v>
@@ -4850,7 +4856,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -4876,14 +4882,14 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>74</v>
@@ -4932,7 +4938,7 @@
         <v>74</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>72</v>
